--- a/SGC-CKN/Excel/571965b2-0b8f-4619-b387-5b13384adb7b_Trụ_HN_P477_C1_D2000_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/571965b2-0b8f-4619-b387-5b13384adb7b_Trụ_HN_P477_C1_D2000_12-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -38,7 +38,7 @@
     <t>C1</t>
   </si>
   <si>
-    <t>Biên bản số</t>
+    <t>Tên Máy khoan</t>
   </si>
   <si>
     <t/>
@@ -95,7 +95,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Cát mịn màu xám nâu lẫn bùn sét, kết cấu xốp</t>
+    <t>Cát mịn lẫn bụi, lẫn vỏ sò, màu xám nâu, xám ghi, kết cấu xốp đến chặt vừa</t>
   </si>
   <si>
     <t xml:space="preserve">09:45
@@ -139,7 +139,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Cát, san, sỏi nhỏ màu xám ghi, kết cấu chặt vừa</t>
+    <t>Cát, sạn, sỏi nhỏ màu xám ghi, kết cấu chặt vừa</t>
   </si>
   <si>
     <t xml:space="preserve">13:30
@@ -150,12 +150,6 @@
 09/03/2026</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Chưa xác định (Lớp 7)</t>
-  </si>
-  <si>
     <t xml:space="preserve">14:10
 09/03/2026</t>
   </si>
@@ -178,7 +172,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội, sỏi, sạn cát kết cấu chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:00
@@ -194,9 +188,6 @@
   </si>
   <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, kết cấu rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">19:05
@@ -284,7 +275,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -335,21 +326,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF4C1D95"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF365314"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF7C2D12"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -362,7 +338,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,21 +388,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDD6FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9F99D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
     <fill>
@@ -522,7 +483,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -578,40 +539,13 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1461,614 +1395,614 @@
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="16">
+      <c r="F19" s="13">
         <v>-22.5</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="13">
         <v>-24.5</v>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="13">
         <v>0.42</v>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="13">
         <v>2</v>
       </c>
       <c r="J19" s="12">
         <v>4.8</v>
       </c>
-      <c r="K19" s="17" t="s">
-        <v>45</v>
+      <c r="K19" s="14" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="19">
+      <c r="F20" s="13">
         <v>-24.5</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="13">
         <v>-26.5</v>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="13">
         <v>0.42</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="13">
         <v>2</v>
       </c>
       <c r="J20" s="12">
         <v>4.8</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="20" t="s">
+      <c r="B21" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="19">
+      <c r="D21" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="13">
         <v>-26.5</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="13">
         <v>-28.5</v>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="13">
         <v>0.42</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="13">
         <v>2</v>
       </c>
       <c r="J21" s="12">
         <v>4.8</v>
       </c>
-      <c r="K21" s="20" t="s">
+      <c r="K21" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="20" t="s">
+      <c r="B22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="19">
+      <c r="D22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="13">
         <v>-28.5</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="13">
         <v>-30.8</v>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="13">
         <v>0.5</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="13">
         <v>2.3</v>
       </c>
       <c r="J22" s="12">
         <v>4.6</v>
       </c>
-      <c r="K22" s="20" t="s">
+      <c r="K22" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="23" t="s">
+      <c r="E23" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F23" s="22">
+      <c r="F23" s="16">
         <v>-30.8</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="16">
         <v>-32.8</v>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="16">
         <v>0.33</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="16">
         <v>2</v>
       </c>
       <c r="J23" s="8">
         <v>6</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="K23" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="23" t="s">
+      <c r="A24" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="22">
+      <c r="E24" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="16">
         <v>-32.8</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="16">
         <v>-34.8</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="16">
         <v>0.33</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="16">
         <v>2</v>
       </c>
       <c r="J24" s="8">
         <v>6</v>
       </c>
-      <c r="K24" s="23" t="s">
+      <c r="K24" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="27" t="s">
+      <c r="A25" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" s="25">
+      <c r="F25" s="16">
         <v>-34.8</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="16">
         <v>-36.8</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="16">
         <v>0.42</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="16">
         <v>2</v>
       </c>
       <c r="J25" s="12">
         <v>4.8</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="25">
+      <c r="F26" s="16">
         <v>-36.8</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="16">
         <v>-38.8</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="16">
         <v>0.92</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="16">
         <v>2</v>
       </c>
       <c r="J26" s="12">
         <v>2.18</v>
       </c>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="26" t="s">
+      <c r="E27" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="F27" s="25">
+      <c r="F27" s="16">
         <v>-38.8</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="16">
         <v>-40.8</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H27" s="16">
         <v>0.42</v>
       </c>
-      <c r="I27" s="25">
+      <c r="I27" s="16">
         <v>2</v>
       </c>
       <c r="J27" s="12">
         <v>4.8</v>
       </c>
-      <c r="K27" s="26" t="s">
+      <c r="K27" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="26" t="s">
+      <c r="A28" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="25">
+      <c r="E28" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="16">
         <v>-40.8</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="16">
         <v>-42.8</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="16">
         <v>0.42</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="16">
         <v>2</v>
       </c>
       <c r="J28" s="12">
         <v>4.8</v>
       </c>
-      <c r="K28" s="26" t="s">
+      <c r="K28" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" s="25">
+      <c r="A29" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="16">
         <v>-42.8</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="16">
         <v>-44.8</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="16">
         <v>0.83</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="16">
         <v>2</v>
       </c>
       <c r="J29" s="12">
         <v>2.4</v>
       </c>
-      <c r="K29" s="26" t="s">
+      <c r="K29" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="25">
+      <c r="A30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="16">
         <v>-44.8</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="16">
         <v>-46.8</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="16">
         <v>0.83</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="16">
         <v>2</v>
       </c>
       <c r="J30" s="12">
         <v>2.4</v>
       </c>
-      <c r="K30" s="26" t="s">
+      <c r="K30" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F31" s="25">
+      <c r="A31" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="16">
         <v>-46.8</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="16">
         <v>-48.8</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="16">
         <v>1.5</v>
       </c>
-      <c r="I31" s="25">
+      <c r="I31" s="16">
         <v>2</v>
       </c>
       <c r="J31" s="12">
         <v>1.33</v>
       </c>
-      <c r="K31" s="26" t="s">
+      <c r="K31" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="25">
+      <c r="A32" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="16">
         <v>-48.8</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="16">
         <v>-51.8</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="16">
         <v>0.67</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="16">
         <v>3</v>
       </c>
       <c r="J32" s="12">
         <v>4.5</v>
       </c>
-      <c r="K32" s="26" t="s">
-        <v>65</v>
+      <c r="K32" s="17" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" s="25">
+      <c r="A33" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F33" s="16">
         <v>-51.8</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="16">
         <v>-53.8</v>
       </c>
-      <c r="H33" s="25">
+      <c r="H33" s="16">
         <v>0.42</v>
       </c>
-      <c r="I33" s="25">
+      <c r="I33" s="16">
         <v>2</v>
       </c>
       <c r="J33" s="12">
         <v>4.8</v>
       </c>
-      <c r="K33" s="26" t="s">
+      <c r="K33" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="25">
+      <c r="A34" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="16">
         <v>-53.8</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="16">
         <v>-56</v>
       </c>
-      <c r="H34" s="25">
+      <c r="H34" s="16">
         <v>0.58</v>
       </c>
-      <c r="I34" s="25">
+      <c r="I34" s="16">
         <v>2.2</v>
       </c>
       <c r="J34" s="12">
         <v>3.77</v>
       </c>
-      <c r="K34" s="26" t="s">
+      <c r="K34" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="25">
+      <c r="A35" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F35" s="16">
         <v>-56</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="16">
         <v>-57.1</v>
       </c>
-      <c r="H35" s="25">
+      <c r="H35" s="16">
         <v>0.75</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="16">
         <v>1.1</v>
       </c>
       <c r="J35" s="12">
         <v>1.47</v>
       </c>
-      <c r="K35" s="26" t="s">
+      <c r="K35" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
+      <c r="A38" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
     </row>
     <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2150,7 +2084,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2163,31 +2097,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2259,22 +2193,22 @@
         <v>39</v>
       </c>
       <c r="D4" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" s="13">
         <v>-18.5</v>
       </c>
       <c r="F4" s="13">
-        <v>-22.5</v>
+        <v>-30.8</v>
       </c>
       <c r="G4" s="13">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="H4" s="13">
-        <v>4</v>
+        <v>12.3</v>
       </c>
       <c r="I4" s="8">
-        <v>8</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2285,140 +2219,53 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D5" s="16">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E5" s="16">
-        <v>-22.5</v>
+        <v>-30.8</v>
       </c>
       <c r="F5" s="16">
-        <v>-24.5</v>
+        <v>-57.1</v>
       </c>
       <c r="G5" s="16">
-        <v>0.42</v>
+        <v>8.42</v>
       </c>
       <c r="H5" s="16">
-        <v>2</v>
+        <v>26.3</v>
       </c>
       <c r="I5" s="12">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="19">
-        <v>3</v>
-      </c>
-      <c r="E6" s="19">
-        <v>-24.5</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-30.8</v>
-      </c>
-      <c r="G6" s="19">
-        <v>1.33</v>
-      </c>
-      <c r="H6" s="19">
-        <v>6.3</v>
-      </c>
-      <c r="I6" s="12">
-        <v>4.72</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
-        <v>6</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="22">
-        <v>2</v>
-      </c>
-      <c r="E7" s="22">
-        <v>-30.8</v>
-      </c>
-      <c r="F7" s="22">
-        <v>-34.8</v>
-      </c>
-      <c r="G7" s="22">
-        <v>0.67</v>
-      </c>
-      <c r="H7" s="22">
-        <v>4</v>
-      </c>
-      <c r="I7" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
-        <v>7</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="25">
-        <v>11</v>
-      </c>
-      <c r="E8" s="25">
-        <v>-34.8</v>
-      </c>
-      <c r="F8" s="25">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="21">
+        <v>25</v>
+      </c>
+      <c r="E6" s="21">
+        <v>-6.2</v>
+      </c>
+      <c r="F6" s="21">
         <v>-57.1</v>
       </c>
-      <c r="G8" s="25">
-        <v>7.75</v>
-      </c>
-      <c r="H8" s="25">
-        <v>22.3</v>
-      </c>
-      <c r="I8" s="12">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="30">
-        <v>25</v>
-      </c>
-      <c r="E9" s="30">
-        <v>-6.2</v>
-      </c>
-      <c r="F9" s="30">
-        <v>-57.1</v>
-      </c>
-      <c r="G9" s="30">
+      <c r="G6" s="21">
         <v>12.17</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H6" s="21">
         <v>50.9</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I6" s="21">
         <v>4.18</v>
       </c>
     </row>
